--- a/history_prices/APR/prices_13042026.xlsx
+++ b/history_prices/APR/prices_13042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8547887C-0679-49DA-AE3E-79B22F9B1283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB054AD-F9AA-4E45-B413-5F81981E1544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,9 +690,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -725,9 +725,9 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3829,7 +3829,7 @@
         <v>14</v>
       </c>
       <c r="E81" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F81" s="2">
         <v>1.736</v>
@@ -3858,7 +3858,7 @@
         <v>19</v>
       </c>
       <c r="E82" s="4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F82" s="2">
         <v>1.4059999999999999</v>

--- a/history_prices/APR/prices_13042026.xlsx
+++ b/history_prices/APR/prices_13042026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB054AD-F9AA-4E45-B413-5F81981E1544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19B6BFE-5E4E-4808-B3A4-8F95D5BF0463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЕКО БЮЛЕТИН" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1392,10 +1392,11 @@
         <v>1.736</v>
       </c>
       <c r="G10" s="2">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H10" s="3">
-        <v>1.756</v>
+        <f>F10+G10</f>
+        <v>1.766</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
